--- a/Commande/Commande_DigiKey.xlsx
+++ b/Commande/Commande_DigiKey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enseafr-my.sharepoint.com/personal/leo_mollet_ensea_fr/Documents/S2/Electronique 2/Projet/Projet_1DA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enseafr-my.sharepoint.com/personal/leo_mollet_ensea_fr/Documents/S2/Electronique 2/Projet/Projet_1DA/Commande/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="13" documentId="11_81CAA56BE52930F349D05721FA722B44D1D68F10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{602D792A-504C-4511-BC37-13A79464CE37}"/>
@@ -544,6 +544,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
